--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407348.3800616427</v>
+        <v>407348</v>
       </c>
       <c r="R3" t="n">
-        <v>6450313.258692283</v>
+        <v>6450313</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1995-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +895,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>96659</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407348.3800616427</v>
+        <v>407348</v>
       </c>
       <c r="R4" t="n">
-        <v>6450313.258692283</v>
+        <v>6450313</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +960,9 @@
           <t>1995-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1995-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1142,12 +1112,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>107844</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406948.7517771402</v>
+        <v>406949</v>
       </c>
       <c r="R6" t="n">
-        <v>6450308.378189559</v>
+        <v>6450308</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1212,19 +1177,9 @@
           <t>1994-04-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1994-04-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1263,12 +1218,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>107844</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407348.3800616427</v>
+        <v>407348</v>
       </c>
       <c r="R7" t="n">
-        <v>6450313.258692283</v>
+        <v>6450313</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1333,19 +1283,9 @@
           <t>1994-04-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1994-04-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407348.3800616427</v>
+        <v>407348</v>
       </c>
       <c r="R2" t="n">
-        <v>6450313.258692283</v>
+        <v>6450313</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -996,12 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407348.3800616427</v>
+        <v>407348</v>
       </c>
       <c r="R5" t="n">
-        <v>6450313.258692283</v>
+        <v>6450313</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1066,19 +1046,9 @@
           <t>1995-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1995-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101657</v>
+        <v>101665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98904</v>
+        <v>98912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110300</v>
+        <v>110315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110300</v>
+        <v>110315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98912</v>
+        <v>98918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110315</v>
+        <v>110324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110315</v>
+        <v>110324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110324</v>
+        <v>110337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110324</v>
+        <v>110337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110337</v>
+        <v>110346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110337</v>
+        <v>110346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110346</v>
+        <v>110351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110346</v>
+        <v>110351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110351</v>
+        <v>110379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110351</v>
+        <v>110379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100713</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101712</v>
+        <v>101725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110379</v>
+        <v>110392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110379</v>
+        <v>110392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98966</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110392</v>
+        <v>110396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110392</v>
+        <v>110396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5231828</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2345159</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>5060273</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110396</v>
+        <v>110404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110396</v>
+        <v>110404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30609-2025 artfynd.xlsx
+++ b/artfynd/A 30609-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5231828</v>
+        <v>2345159</v>
       </c>
       <c r="B2" t="n">
-        <v>100740</v>
+        <v>99456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -779,11 +779,11 @@
         <v>3838488</v>
       </c>
       <c r="B3" t="n">
-        <v>101739</v>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2345159</v>
+        <v>5060273</v>
       </c>
       <c r="B4" t="n">
-        <v>98980</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5060273</v>
+        <v>5231828</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
         <v>5295842</v>
       </c>
       <c r="B6" t="n">
-        <v>110407</v>
+        <v>111019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>5295843</v>
       </c>
       <c r="B7" t="n">
-        <v>110407</v>
+        <v>111019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56323384</v>
+        <v>56323334</v>
       </c>
       <c r="B8" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,14 +1325,14 @@
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BERGSGÅRDEN, 400 m NNV om , Vg</t>
+          <t>BERGSGÅRDEN, 400 m NO om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406943.9982618534</v>
+        <v>407344</v>
       </c>
       <c r="R8" t="n">
-        <v>6450308.489781625</v>
+        <v>6450313</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1364,7 +1359,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OV-Fal-0600</t>
+          <t>Arkiv-OV-Fal-0421</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1372,19 +1367,9 @@
           <t>1994-04-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1994-04-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1414,21 +1399,16 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56323334</v>
+        <v>56323384</v>
       </c>
       <c r="B9" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,14 +1439,14 @@
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BERGSGÅRDEN, 400 m NO om, Vg</t>
+          <t>BERGSGÅRDEN, 400 m NNV om , Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407343.6142334286</v>
+        <v>406944</v>
       </c>
       <c r="R9" t="n">
-        <v>6450312.842625314</v>
+        <v>6450308</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1493,7 +1473,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>OV-Fal-0599</t>
+          <t>Arkiv-OV-Fal-0422</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1501,19 +1481,9 @@
           <t>1994-04-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1994-04-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1543,7 +1513,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
